--- a/artfynd/A 63584-2025 artfynd.xlsx
+++ b/artfynd/A 63584-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88920</v>
+        <v>88903</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Acksjön, Björsbo (delomr 11), Vstm</t>
+          <t>Acksjön, SO Gräskärret (delomr 8), Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591278.9688555717</v>
+        <v>591552</v>
       </c>
       <c r="R2" t="n">
-        <v>6665197.846938489</v>
+        <v>6665459</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,53 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3024434</v>
+        <v>88911</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Acksjön (delomr 7), Vstm</t>
+          <t>Acksjön, SV Gräskärret (delomr 11), Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591525.5258730205</v>
+        <v>591189</v>
       </c>
       <c r="R3" t="n">
-        <v>6665387.006896006</v>
+        <v>6665347</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,19 +844,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88903</v>
+        <v>88912</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,14 +908,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Acksjön, SO Gräskärret (delomr 8), Vstm</t>
+          <t>Acksjön, SV Gräskärret (delomr 11), Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591551.7047591598</v>
+        <v>591193</v>
       </c>
       <c r="R4" t="n">
-        <v>6665458.971192854</v>
+        <v>6665362</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88917</v>
+        <v>88914</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1009,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Acksjön, Björsbo (delomr 11), Vstm</t>
+          <t>Acksjön, S om Gräskärret (delomr 11), Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591360.1806073517</v>
+        <v>591267</v>
       </c>
       <c r="R5" t="n">
-        <v>6665266.693305473</v>
+        <v>6665371</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,53 +1079,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16950988</v>
+        <v>88917</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lund, 1,4 km VSV om (knärot), Vstm</t>
+          <t>Acksjön, Björsbo (delomr 11), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591396.555864026</v>
+        <v>591360</v>
       </c>
       <c r="R6" t="n">
-        <v>6665310.486696571</v>
+        <v>6665267</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,29 +1142,14 @@
           <t>Möklinta</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>U-Sal-0151</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-06-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-06-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-11-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,24 +1160,737 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88918</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97358</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>53</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Acksjön, Björsbo (delomr 11), Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>591371</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6665208</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2007-11-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>88919</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97358</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Acksjön, Björsbo (delomr 11), Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>591335</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6665198</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2007-11-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>88920</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97358</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>53</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Acksjön, Björsbo (delomr 11), Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>591279</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6665198</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2007-11-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>441268</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Acksjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>591113</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6665074</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2007-11-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3024434</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Acksjön (delomr 7), Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>591526</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6665387</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2007-11-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6989849</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Boda, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>591397</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6665311</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2013-06-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mårten Berglind</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mårten Berglind</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>16950988</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lund, 1,4 km VSV om (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>591397</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6665310</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>U-Sal-0151</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2013-06-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2013-06-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Einar Marklund</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Mårten Berglind</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 63584-2025 artfynd.xlsx
+++ b/artfynd/A 63584-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88903</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88911</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88912</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88917</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88918</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88919</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88920</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/441268</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3024434</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6989849</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,8 +1955,27 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16950988</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>